--- a/resources/demographics.xlsx
+++ b/resources/demographics.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10503"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="S:\AG\AG-Finke\Daten\Ritter_MRI\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/brainsimulation/Desktop/NMDARE_Project/dicom/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D6A9048-07C3-3147-A642-58AEA8F2B93C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="17295" windowHeight="10200"/>
+    <workbookView xWindow="16900" yWindow="660" windowWidth="16560" windowHeight="18460" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -290,7 +291,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -355,7 +356,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Standard" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -632,14 +633,14 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J82"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="22.7109375" customWidth="1"/>
+    <col min="1" max="1" width="22.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -653,12 +654,12 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>9</v>
       </c>
       <c r="B2">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C2" t="s">
         <v>42</v>
@@ -667,26 +668,26 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>10</v>
       </c>
       <c r="B3">
-        <v>59</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>42</v>
+        <v>4</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C4" t="s">
         <v>4</v>
@@ -695,12 +696,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5">
-        <v>60</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>42</v>
@@ -709,12 +710,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>13</v>
       </c>
       <c r="B6">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="C6" t="s">
         <v>42</v>
@@ -723,12 +724,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>14</v>
       </c>
       <c r="B7">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C7" t="s">
         <v>42</v>
@@ -737,12 +738,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>15</v>
       </c>
       <c r="B8">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>42</v>
@@ -751,12 +752,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C9" t="s">
         <v>4</v>
@@ -765,12 +766,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>17</v>
       </c>
       <c r="B10">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C10" t="s">
         <v>4</v>
@@ -779,12 +780,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>18</v>
       </c>
       <c r="B11">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
         <v>4</v>
@@ -793,12 +794,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>19</v>
       </c>
       <c r="B12">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C12" t="s">
         <v>4</v>
@@ -807,12 +808,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>20</v>
       </c>
       <c r="B13">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
         <v>42</v>
@@ -821,12 +822,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>21</v>
       </c>
       <c r="B14">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
@@ -835,12 +836,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
         <v>22</v>
       </c>
       <c r="B15">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C15" t="s">
         <v>42</v>
@@ -849,12 +850,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>23</v>
       </c>
       <c r="B16">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="C16" t="s">
         <v>42</v>
@@ -863,12 +864,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>24</v>
       </c>
       <c r="B17">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C17" t="s">
         <v>42</v>
@@ -877,12 +878,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A18" t="s">
         <v>25</v>
       </c>
       <c r="B18">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="C18" t="s">
         <v>42</v>
@@ -891,12 +892,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>26</v>
       </c>
       <c r="B19">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="C19" t="s">
         <v>42</v>
@@ -905,12 +906,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>27</v>
       </c>
       <c r="B20">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="C20" t="s">
         <v>42</v>
@@ -919,12 +920,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>28</v>
       </c>
       <c r="B21">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C21" t="s">
         <v>42</v>
@@ -933,7 +934,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
         <v>29</v>
       </c>
@@ -947,12 +948,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
         <v>30</v>
       </c>
       <c r="B23">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="C23" t="s">
         <v>4</v>
@@ -961,12 +962,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A24" t="s">
         <v>31</v>
       </c>
       <c r="B24">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="C24" t="s">
         <v>4</v>
@@ -975,12 +976,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A25" t="s">
         <v>7</v>
       </c>
       <c r="B25">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
         <v>42</v>
@@ -989,12 +990,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A26" t="s">
         <v>8</v>
       </c>
       <c r="B26">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="C26" t="s">
         <v>42</v>
@@ -1003,12 +1004,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A27" t="s">
         <v>83</v>
       </c>
       <c r="B27">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="C27" t="s">
         <v>4</v>
@@ -1017,12 +1018,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A28" t="s">
         <v>84</v>
       </c>
       <c r="B28">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
         <v>4</v>
@@ -1031,7 +1032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A29" t="s">
         <v>85</v>
       </c>
@@ -1045,12 +1046,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A30" t="s">
         <v>86</v>
       </c>
       <c r="B30">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C30" t="s">
         <v>42</v>
@@ -1059,12 +1060,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A31" t="s">
         <v>32</v>
       </c>
       <c r="B31">
-        <v>31</v>
+        <v>21</v>
       </c>
       <c r="C31" t="s">
         <v>42</v>
@@ -1073,12 +1074,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A32" t="s">
         <v>33</v>
       </c>
       <c r="B32">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C32" t="s">
         <v>42</v>
@@ -1087,12 +1088,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A33" t="s">
         <v>34</v>
       </c>
       <c r="B33">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="C33" t="s">
         <v>42</v>
@@ -1101,12 +1102,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A34" t="s">
         <v>35</v>
       </c>
       <c r="B34">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
         <v>42</v>
@@ -1115,12 +1116,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A35" t="s">
         <v>36</v>
       </c>
       <c r="B35">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="C35" t="s">
         <v>42</v>
@@ -1129,12 +1130,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A36" t="s">
         <v>37</v>
       </c>
       <c r="B36">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="C36" t="s">
         <v>42</v>
@@ -1143,12 +1144,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
         <v>38</v>
       </c>
       <c r="B37">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="C37" t="s">
         <v>42</v>
@@ -1157,12 +1158,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
         <v>39</v>
       </c>
       <c r="B38">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="C38" t="s">
         <v>42</v>
@@ -1171,12 +1172,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
         <v>40</v>
       </c>
       <c r="B39">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="C39" t="s">
         <v>42</v>
@@ -1185,7 +1186,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
         <v>5</v>
       </c>
@@ -1199,7 +1200,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
         <v>6</v>
       </c>
@@ -1213,7 +1214,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A42" s="1" t="s">
         <v>41</v>
       </c>
@@ -1227,7 +1228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A43" s="1" t="s">
         <v>43</v>
       </c>
@@ -1242,7 +1243,7 @@
       </c>
       <c r="J43" s="4"/>
     </row>
-    <row r="44" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A44" s="1" t="s">
         <v>44</v>
       </c>
@@ -1256,7 +1257,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A45" s="1" t="s">
         <v>45</v>
       </c>
@@ -1270,7 +1271,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
@@ -1284,7 +1285,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A47" s="1" t="s">
         <v>47</v>
       </c>
@@ -1298,7 +1299,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A48" s="1" t="s">
         <v>48</v>
       </c>
@@ -1312,7 +1313,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A49" s="1" t="s">
         <v>49</v>
       </c>
@@ -1326,7 +1327,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A50" s="1" t="s">
         <v>50</v>
       </c>
@@ -1340,7 +1341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A51" s="1" t="s">
         <v>51</v>
       </c>
@@ -1354,7 +1355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A52" s="1" t="s">
         <v>52</v>
       </c>
@@ -1368,7 +1369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A53" s="1" t="s">
         <v>53</v>
       </c>
@@ -1382,7 +1383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A54" s="1" t="s">
         <v>54</v>
       </c>
@@ -1396,7 +1397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A55" s="1" t="s">
         <v>55</v>
       </c>
@@ -1410,7 +1411,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A56" s="1" t="s">
         <v>56</v>
       </c>
@@ -1424,7 +1425,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A57" s="1" t="s">
         <v>57</v>
       </c>
@@ -1438,7 +1439,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A58" s="1" t="s">
         <v>58</v>
       </c>
@@ -1452,7 +1453,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A59" s="1" t="s">
         <v>59</v>
       </c>
@@ -1466,7 +1467,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A60" s="1" t="s">
         <v>60</v>
       </c>
@@ -1480,7 +1481,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A61" s="1" t="s">
         <v>61</v>
       </c>
@@ -1494,7 +1495,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A62" s="1" t="s">
         <v>62</v>
       </c>
@@ -1508,7 +1509,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A63" s="5" t="s">
         <v>63</v>
       </c>
@@ -1522,7 +1523,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A64" s="1" t="s">
         <v>64</v>
       </c>
@@ -1536,7 +1537,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A65" s="1" t="s">
         <v>65</v>
       </c>
@@ -1550,7 +1551,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A66" s="1" t="s">
         <v>66</v>
       </c>
@@ -1564,7 +1565,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A67" s="1" t="s">
         <v>67</v>
       </c>
@@ -1578,7 +1579,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A68" s="1" t="s">
         <v>68</v>
       </c>
@@ -1592,7 +1593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A69" s="1" t="s">
         <v>69</v>
       </c>
@@ -1606,7 +1607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A70" s="1" t="s">
         <v>70</v>
       </c>
@@ -1620,7 +1621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A71" s="1" t="s">
         <v>71</v>
       </c>
@@ -1634,7 +1635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A72" s="1" t="s">
         <v>72</v>
       </c>
@@ -1648,7 +1649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A73" s="1" t="s">
         <v>73</v>
       </c>
@@ -1662,7 +1663,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A74" s="1" t="s">
         <v>74</v>
       </c>
@@ -1676,7 +1677,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A75" s="1" t="s">
         <v>75</v>
       </c>
@@ -1690,7 +1691,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A76" s="1" t="s">
         <v>76</v>
       </c>
@@ -1704,7 +1705,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A77" s="1" t="s">
         <v>77</v>
       </c>
@@ -1718,7 +1719,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A78" s="1" t="s">
         <v>78</v>
       </c>
@@ -1732,7 +1733,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A79" s="1" t="s">
         <v>79</v>
       </c>
@@ -1746,7 +1747,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A80" s="1" t="s">
         <v>80</v>
       </c>
@@ -1760,7 +1761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A81" s="1" t="s">
         <v>81</v>
       </c>
@@ -1774,7 +1775,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A82" s="1" t="s">
         <v>82</v>
       </c>
